--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 17.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 17.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.09.2026</t>
+          <t>Open Line FR Report - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -571,19 +571,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,992
-Cr. 7.80</t>
+          <t>81,555
+Cr. 8.16</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-82,911
-Cr. -8.29</t>
+          <t>-79,348
+Cr. -7.93</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.69</t>
         </is>
       </c>
     </row>
@@ -606,19 +606,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>11,801
-Cr. 1.18</t>
+          <t>12,549
+Cr. 1.25</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-20,426
-Cr. -2.04</t>
+          <t>-19,678
+Cr. -1.97</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>38.94</t>
         </is>
       </c>
     </row>
@@ -641,19 +641,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,289
-Cr. 5.73</t>
+          <t>64,226
+Cr. 6.42</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,029
-Cr. -6.30</t>
+          <t>-56,092
+Cr. -5.61</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>53.38</t>
         </is>
       </c>
     </row>
@@ -676,19 +676,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>363,937
-Cr. 36.39</t>
+          <t>376,586
+Cr. 37.66</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-143,483
-Cr. -14.35</t>
+          <t>-130,834
+Cr. -13.08</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>74.22</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,692,699
-Cr. 369.27</t>
+          <t>3,758,184
+Cr. 375.82</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>729,904
-Cr. 72.99</t>
+          <t>795,389
+Cr. 79.54</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124.64</t>
+          <t>126.85</t>
         </is>
       </c>
     </row>
@@ -746,19 +746,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>151,197
-Cr. 15.12</t>
+          <t>164,242
+Cr. 16.42</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,930
-Cr. 1.89</t>
+          <t>31,975
+Cr. 3.20</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>124.17</t>
         </is>
       </c>
     </row>
@@ -781,19 +781,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>123,038
-Cr. 12.30</t>
+          <t>139,533
+Cr. 13.95</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-399,805
-Cr. -39.98</t>
+          <t>-383,310
+Cr. -38.33</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>26.69</t>
         </is>
       </c>
     </row>
@@ -816,19 +816,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,924
-Cr. 9.49</t>
+          <t>104,326
+Cr. 10.43</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,919
-Cr. -21.29</t>
+          <t>-203,517
+Cr. -20.35</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>33.89</t>
         </is>
       </c>
     </row>
@@ -921,19 +921,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,129
-Cr. 0.51</t>
+          <t>5,681
+Cr. 0.57</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,573
-Cr. -4.86</t>
+          <t>-48,021
+Cr. -4.80</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>10.58</t>
         </is>
       </c>
     </row>
@@ -991,19 +991,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>131,048
-Cr. 13.10</t>
+          <t>139,726
+Cr. 13.97</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-179,864
-Cr. -17.99</t>
+          <t>-171,186
+Cr. -17.12</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>44.94</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>103,375
-Cr. 10.34</t>
+          <t>112,585
+Cr. 11.26</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-212,358
-Cr. -21.24</t>
+          <t>-203,148
+Cr. -20.31</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>35.66</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,896,554
-Cr. 489.66</t>
+          <t>5,043,318
+Cr. 504.33</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-711,147
-Cr. -71.11</t>
+          <t>-564,383
+Cr. -56.44</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>89.94</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1275,24 +1275,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>408,842
-Cr. 40.88</t>
+          <t>441,204
+Cr. 44.12</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>609,511
-Cr. 60.95</t>
+          <t>577,149
+Cr. 57.71</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>56.67</t>
         </is>
       </c>
     </row>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,746,106
-Cr. 374.61</t>
+          <t>3,802,846
+Cr. 380.28</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-628,591
-Cr. -62.86</t>
+          <t>-685,331
+Cr. -68.53</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>121.98</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-21.98</t>
         </is>
       </c>
     </row>
@@ -1485,24 +1485,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>707,656
-Cr. 70.77</t>
+          <t>765,318
+Cr. 76.53</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>593,353
-Cr. 59.34</t>
+          <t>535,691
+Cr. 53.57</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>41.18</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 05.09.2026</t>
+          <t>GSU FR Report - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2032,19 +2032,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>317,088
-Cr. 31.71</t>
+          <t>342,792
+Cr. 34.28</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-129,512
-Cr. -12.95</t>
+          <t>-103,808
+Cr. -10.38</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>76.76</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>319,263
-Cr. 31.93</t>
+          <t>344,967
+Cr. 34.50</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-132,340
-Cr. -13.23</t>
+          <t>-106,636
+Cr. -10.66</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>76.39</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 05.09.2026</t>
+          <t>GSU FR Fund Wise - As On 17.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>319,136
-Cr. 31.91</t>
+          <t>344,840
+Cr. 34.48</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>132,465
-Cr. 13.25</t>
+          <t>106,761
+Cr. 10.68</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>23.64</t>
         </is>
       </c>
     </row>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 17." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 17.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 17.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 17.09.2026</t>
+          <t>Open Line FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -571,19 +571,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>81,555
-Cr. 8.16</t>
+          <t>77,992
+Cr. 7.80</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-79,348
-Cr. -7.93</t>
+          <t>-82,911
+Cr. -8.29</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>48.47</t>
         </is>
       </c>
     </row>
@@ -606,19 +606,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>12,549
-Cr. 1.25</t>
+          <t>11,801
+Cr. 1.18</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-19,678
-Cr. -1.97</t>
+          <t>-20,426
+Cr. -2.04</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>36.62</t>
         </is>
       </c>
     </row>
@@ -641,19 +641,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>64,226
-Cr. 6.42</t>
+          <t>57,289
+Cr. 5.73</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-56,092
-Cr. -5.61</t>
+          <t>-63,029
+Cr. -6.30</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>47.61</t>
         </is>
       </c>
     </row>
@@ -676,19 +676,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>376,586
-Cr. 37.66</t>
+          <t>363,937
+Cr. 36.39</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-130,834
-Cr. -13.08</t>
+          <t>-143,483
+Cr. -14.35</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.22</t>
+          <t>71.72</t>
         </is>
       </c>
     </row>
@@ -711,19 +711,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,758,184
-Cr. 375.82</t>
+          <t>3,692,699
+Cr. 369.27</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>795,389
-Cr. 79.54</t>
+          <t>729,904
+Cr. 72.99</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>126.85</t>
+          <t>124.64</t>
         </is>
       </c>
     </row>
@@ -746,19 +746,19 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>164,242
-Cr. 16.42</t>
+          <t>151,197
+Cr. 15.12</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>31,975
-Cr. 3.20</t>
+          <t>18,930
+Cr. 1.89</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>114.31</t>
         </is>
       </c>
     </row>
@@ -781,19 +781,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>139,533
-Cr. 13.95</t>
+          <t>123,038
+Cr. 12.30</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-383,310
-Cr. -38.33</t>
+          <t>-399,805
+Cr. -39.98</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>23.53</t>
         </is>
       </c>
     </row>
@@ -816,19 +816,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>104,326
-Cr. 10.43</t>
+          <t>94,924
+Cr. 9.49</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-203,517
-Cr. -20.35</t>
+          <t>-212,919
+Cr. -21.29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>30.84</t>
         </is>
       </c>
     </row>
@@ -921,19 +921,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,681
-Cr. 0.57</t>
+          <t>5,129
+Cr. 0.51</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,021
-Cr. -4.80</t>
+          <t>-48,573
+Cr. -4.86</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>9.55</t>
         </is>
       </c>
     </row>
@@ -991,19 +991,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>139,726
-Cr. 13.97</t>
+          <t>131,048
+Cr. 13.10</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-171,186
-Cr. -17.12</t>
+          <t>-179,864
+Cr. -17.99</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>42.15</t>
         </is>
       </c>
     </row>
@@ -1061,19 +1061,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>112,585
-Cr. 11.26</t>
+          <t>103,375
+Cr. 10.34</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-203,148
-Cr. -20.31</t>
+          <t>-212,358
+Cr. -21.24</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>32.74</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>5,043,318
-Cr. 504.33</t>
+          <t>4,896,554
+Cr. 489.66</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-564,383
-Cr. -56.44</t>
+          <t>-711,147
+Cr. -71.11</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>87.32</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 17.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1275,24 +1275,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>441,204
-Cr. 44.12</t>
+          <t>408,842
+Cr. 40.88</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>577,149
-Cr. 57.71</t>
+          <t>609,511
+Cr. 60.95</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>59.85</t>
         </is>
       </c>
     </row>
@@ -1415,24 +1415,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,802,846
-Cr. 380.28</t>
+          <t>3,746,106
+Cr. 374.61</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-685,331
-Cr. -68.53</t>
+          <t>-628,591
+Cr. -62.86</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>121.98</t>
+          <t>120.16</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-21.98</t>
+          <t>-20.16</t>
         </is>
       </c>
     </row>
@@ -1485,24 +1485,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>765,318
-Cr. 76.53</t>
+          <t>707,656
+Cr. 70.77</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>535,691
-Cr. 53.57</t>
+          <t>593,353
+Cr. 59.34</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>54.39</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>45.61</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 17.09.2026</t>
+          <t>GSU FR Report - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2032,19 +2032,19 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>342,792
-Cr. 34.28</t>
+          <t>317,088
+Cr. 31.71</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-103,808
-Cr. -10.38</t>
+          <t>-129,512
+Cr. -12.95</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>71.00</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>344,967
-Cr. 34.50</t>
+          <t>319,263
+Cr. 31.93</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-106,636
-Cr. -10.66</t>
+          <t>-132,340
+Cr. -13.23</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>76.39</t>
+          <t>70.70</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 17.09.2026</t>
+          <t>GSU FR Fund Wise - As On 05.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>344,840
-Cr. 34.48</t>
+          <t>319,136
+Cr. 31.91</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>106,761
-Cr. 10.68</t>
+          <t>132,465
+Cr. 13.25</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>29.33</t>
         </is>
       </c>
     </row>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,20 +565,71 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>160,903
-Cr. 16.09</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>160,903</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>16.09 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77,992
-Cr. 7.80</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>77,992</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.80 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-82,911
-Cr. -8.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-82,911</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -600,20 +651,71 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>32,227
-Cr. 3.22</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>32,227</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3.22 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>11,801
-Cr. 1.18</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,801</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.18 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-20,426
-Cr. -2.04</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-20,426</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.04 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -635,20 +737,71 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>120,318
-Cr. 12.03</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>120,318</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.03 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>57,289
-Cr. 5.73</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>57,289</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.73 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-63,029
-Cr. -6.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-63,029</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -670,20 +823,71 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>507,420
-Cr. 50.74</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>507,420</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>50.74 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>363,937
-Cr. 36.39</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>363,937</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.39 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>-143,483
-Cr. -14.35</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-143,483</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-14.35 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -705,20 +909,71 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2,962,795
-Cr. 296.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,962,795</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>296.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3,692,699
-Cr. 369.27</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,692,699</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>369.27 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>729,904
-Cr. 72.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>729,904</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>72.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -740,20 +995,71 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>132,267
-Cr. 13.23</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>132,267</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.23 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>151,197
-Cr. 15.12</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>151,197</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.12 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>18,930
-Cr. 1.89</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>18,930</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.89 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -775,20 +1081,71 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>522,843
-Cr. 52.28</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>522,843</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>52.28 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>123,038
-Cr. 12.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>123,038</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-399,805
-Cr. -39.98</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-399,805</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-39.98 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -810,20 +1167,71 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>307,843
-Cr. 30.78</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>307,843</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.78 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>94,924
-Cr. 9.49</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>94,924</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.49 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>-212,919
-Cr. -21.29</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-212,919</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.29 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -845,20 +1253,71 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -880,20 +1339,71 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>13,194
-Cr. 1.32</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>13,194</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.32 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>24,273
-Cr. 2.43</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>24,273</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.43 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>11,079
-Cr. 1.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>11,079</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -915,20 +1425,71 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>53,702
-Cr. 5.37</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>53,702</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.37 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5,129
-Cr. 0.51</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,129</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.51 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-48,573
-Cr. -4.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-48,573</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.86 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -950,20 +1511,71 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>97,500
-Cr. 9.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>97,500</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.75 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>59,852
-Cr. 5.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>59,852</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-37,648
-Cr. -3.76</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-37,648</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-3.76 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -985,20 +1597,71 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>310,912
-Cr. 31.09</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>310,912</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.09 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>131,048
-Cr. 13.10</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>131,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.10 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-179,864
-Cr. -17.99</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-179,864</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-17.99 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1020,20 +1683,71 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1055,20 +1769,71 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>315,733
-Cr. 31.57</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>315,733</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.57 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>103,375
-Cr. 10.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>103,375</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.34 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>-212,358
-Cr. -21.24</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-212,358</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.24 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1086,20 +1851,71 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>64,034
-Cr. 6.40</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>64,034</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>-64,034
-Cr. -6.40</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-64,034</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.40 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1121,20 +1937,71 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>6,010
-Cr. 0.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>6,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.60 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-6,010
-Cr. -0.60</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-6,010</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.60 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1152,20 +2019,71 @@
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>5,607,701
-Cr. 560.77</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,607,701</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>560.77 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>4,896,554
-Cr. 489.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>4,896,554</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>489.66 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-711,147
-Cr. -71.11</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-711,147</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-71.11 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1269,20 +2187,71 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1,018,353
-Cr. 101.84</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,018,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>101.84 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>408,842
-Cr. 40.88</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>408,842</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>40.88 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>609,511
-Cr. 60.95</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>609,511</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>60.95 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1304,20 +2273,71 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>40,232
-Cr. 4.02</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>40,232</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.02 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>15,491
-Cr. 1.55</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>15,491</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.55 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>24,741
-Cr. 2.47</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>24,741</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.47 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1339,20 +2359,71 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>130,592
-Cr. 13.06</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>130,592</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.06 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>18,459
-Cr. 1.85</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>18,459</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.85 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>112,133
-Cr. 11.21</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>112,133</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.21 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1374,20 +2445,71 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1409,20 +2531,71 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3,117,515
-Cr. 311.75</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,117,515</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>311.75 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>3,746,106
-Cr. 374.61</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>3,746,106</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>374.61 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-628,591
-Cr. -62.86</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-628,591</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-62.86 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1444,20 +2617,71 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1479,20 +2703,71 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1,301,009
-Cr. 130.10</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1,301,009</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>130.10 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>707,656
-Cr. 70.77</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>707,656</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>70.77 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>593,353
-Cr. 59.34</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>593,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>59.34 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1606,20 +2881,71 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1641,20 +2967,71 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1676,20 +3053,71 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1711,20 +3139,71 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>127
-Cr. 0.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>127</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>126
-Cr. 0.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>126</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1746,20 +3225,71 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1781,20 +3311,71 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1816,20 +3397,71 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1851,20 +3483,71 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1886,20 +3569,71 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1921,20 +3655,71 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>1
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-1
-Cr. -0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1956,20 +3741,71 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5,001
-Cr. 0.50</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>5,001</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.50 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>2,048
-Cr. 0.20</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>2,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.20 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-2,953
-Cr. -0.30</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-2,953</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.30 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1991,20 +3827,71 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2026,20 +3913,71 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>446,600
-Cr. 44.66</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>446,600</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>44.66 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>317,088
-Cr. 31.71</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>317,088</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.71 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-129,512
-Cr. -12.95</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-129,512</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.95 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2061,20 +3999,71 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2096,20 +4085,71 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2127,20 +4167,71 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2162,20 +4253,71 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2193,20 +4335,71 @@
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>451,603
-Cr. 45.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>451,603</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>45.16 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>319,263
-Cr. 31.93</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>319,263</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.93 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-132,340
-Cr. -13.23</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-132,340</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-13.23 Cr</t>
+          </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2310,20 +4503,71 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>451,601
-Cr. 45.16</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>451,601</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>45.16 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>319,136
-Cr. 31.91</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>319,136</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>31.91 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>132,465
-Cr. 13.25</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>132,465</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>13.25 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2345,20 +4589,71 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>1
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2380,20 +4675,71 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2415,20 +4761,71 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2450,20 +4847,71 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2485,20 +4933,71 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>0</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2520,20 +5019,71 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1
-Cr. 0.00</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.00 Cr</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>127
-Cr. 0.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>127</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>-126
-Cr. -0.01</t>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <sz val="11"/>
+            </rPr>
+            <t>-126</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.01 Cr</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.09.2026</t>
+          <t>Open Line FR Report - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -593,19 +593,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>77,992</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.80 Cr</t>
+            <t>81,555</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.16 Cr</t>
           </r>
         </is>
       </c>
@@ -616,25 +616,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-82,911</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-8.29 Cr</t>
+            <t>-79,348</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.93 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.69</t>
         </is>
       </c>
     </row>
@@ -679,19 +679,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,801</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.18 Cr</t>
+            <t>12,767</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.28 Cr</t>
           </r>
         </is>
       </c>
@@ -702,25 +702,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-20,426</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.04 Cr</t>
+            <t>-19,460</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.95 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>39.62</t>
         </is>
       </c>
     </row>
@@ -765,19 +765,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>57,289</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.73 Cr</t>
+            <t>64,676</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>6.47 Cr</t>
           </r>
         </is>
       </c>
@@ -788,25 +788,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-63,029</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-6.30 Cr</t>
+            <t>-55,642</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.56 Cr</t>
           </r>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>53.75</t>
         </is>
       </c>
     </row>
@@ -851,19 +851,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>363,937</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.39 Cr</t>
+            <t>379,202</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.92 Cr</t>
           </r>
         </is>
       </c>
@@ -874,25 +874,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-143,483</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-14.35 Cr</t>
+            <t>-128,218</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.82 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>74.73</t>
         </is>
       </c>
     </row>
@@ -937,19 +937,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,692,699</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>369.27 Cr</t>
+            <t>3,805,865</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>380.59 Cr</t>
           </r>
         </is>
       </c>
@@ -960,25 +960,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>729,904</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>72.99 Cr</t>
+            <t>843,070</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>84.31 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>124.64</t>
+          <t>128.46</t>
         </is>
       </c>
     </row>
@@ -1023,19 +1023,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>151,197</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>15.12 Cr</t>
+            <t>183,938</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.39 Cr</t>
           </r>
         </is>
       </c>
@@ -1046,25 +1046,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,930</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.89 Cr</t>
+            <t>51,671</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>114.31</t>
+          <t>139.07</t>
         </is>
       </c>
     </row>
@@ -1109,19 +1109,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>123,038</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>12.30 Cr</t>
+            <t>140,407</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.04 Cr</t>
           </r>
         </is>
       </c>
@@ -1132,25 +1132,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-399,805</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-39.98 Cr</t>
+            <t>-382,436</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-38.24 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>26.85</t>
         </is>
       </c>
     </row>
@@ -1195,19 +1195,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>94,924</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>9.49 Cr</t>
+            <t>105,095</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.51 Cr</t>
           </r>
         </is>
       </c>
@@ -1218,25 +1218,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-212,919</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.29 Cr</t>
+            <t>-202,748</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.27 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>34.14</t>
         </is>
       </c>
     </row>
@@ -1344,19 +1344,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>13,194</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.32 Cr</t>
+            <t>40,372</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4.04 Cr</t>
           </r>
         </is>
       </c>
@@ -1367,19 +1367,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>24,273</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.43 Cr</t>
+            <t>25,991</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.60 Cr</t>
           </r>
         </is>
       </c>
@@ -1390,25 +1390,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>11,079</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.11 Cr</t>
+            <t>-14,381</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>183.97</t>
+          <t>64.38</t>
         </is>
       </c>
     </row>
@@ -1453,19 +1453,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,129</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.51 Cr</t>
+            <t>5,681</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.57 Cr</t>
           </r>
         </is>
       </c>
@@ -1476,25 +1476,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-48,573</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.86 Cr</t>
+            <t>-48,021</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.80 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>10.58</t>
         </is>
       </c>
     </row>
@@ -1539,19 +1539,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>59,852</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.99 Cr</t>
+            <t>71,111</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.11 Cr</t>
           </r>
         </is>
       </c>
@@ -1562,25 +1562,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-37,648</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-3.76 Cr</t>
+            <t>-26,389</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.64 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>72.93</t>
         </is>
       </c>
     </row>
@@ -1625,19 +1625,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>131,048</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.10 Cr</t>
+            <t>147,126</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>14.71 Cr</t>
           </r>
         </is>
       </c>
@@ -1648,25 +1648,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-179,864</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-17.99 Cr</t>
+            <t>-163,786</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-16.38 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>47.32</t>
         </is>
       </c>
     </row>
@@ -1797,19 +1797,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>103,375</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10.34 Cr</t>
+            <t>112,585</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.26 Cr</t>
           </r>
         </is>
       </c>
@@ -1820,25 +1820,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-212,358</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-21.24 Cr</t>
+            <t>-203,148</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.31 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>35.66</t>
         </is>
       </c>
     </row>
@@ -2024,19 +2024,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,607,701</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>560.77 Cr</t>
+            <t>5,634,879</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>563.49 Cr</t>
           </r>
         </is>
       </c>
@@ -2047,19 +2047,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,896,554</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>489.66 Cr</t>
+            <t>5,135,999</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>513.60 Cr</t>
           </r>
         </is>
       </c>
@@ -2070,25 +2070,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-711,147</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-71.11 Cr</t>
+            <t>-498,880</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-49.89 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.15</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2192,19 +2192,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,018,353</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>101.84 Cr</t>
+            <t>1,045,531</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>104.55 Cr</t>
           </r>
         </is>
       </c>
@@ -2215,19 +2215,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>408,842</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>40.88 Cr</t>
+            <t>457,028</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>45.70 Cr</t>
           </r>
         </is>
       </c>
@@ -2238,30 +2238,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>609,511</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>60.95 Cr</t>
+            <t>588,503</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>58.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>56.29</t>
         </is>
       </c>
     </row>
@@ -2301,19 +2301,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>15,491</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.55 Cr</t>
+            <t>21,238</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.12 Cr</t>
           </r>
         </is>
       </c>
@@ -2324,30 +2324,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>24,741</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.47 Cr</t>
+            <t>18,994</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.90 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>38.50</t>
+          <t>52.79</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>47.21</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2559,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,746,106</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>374.61 Cr</t>
+            <t>3,844,908</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>384.49 Cr</t>
           </r>
         </is>
       </c>
@@ -2582,30 +2582,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-628,591</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-62.86 Cr</t>
+            <t>-727,393</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-72.74 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>120.16</t>
+          <t>123.33</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-20.16</t>
+          <t>-23.33</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>707,656</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>70.77 Cr</t>
+            <t>794,366</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>79.44 Cr</t>
           </r>
         </is>
       </c>
@@ -2754,30 +2754,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>593,353</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>59.34 Cr</t>
+            <t>506,643</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>50.66 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>54.39</t>
+          <t>61.06</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>38.94</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 05.09.2026</t>
+          <t>GSU FR Report - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3941,19 +3941,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>317,088</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.71 Cr</t>
+            <t>366,679</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.67 Cr</t>
           </r>
         </is>
       </c>
@@ -3964,25 +3964,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-129,512</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.95 Cr</t>
+            <t>-79,921</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.99 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>82.10</t>
         </is>
       </c>
     </row>
@@ -4363,19 +4363,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>319,263</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.93 Cr</t>
+            <t>368,854</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.89 Cr</t>
           </r>
         </is>
       </c>
@@ -4386,25 +4386,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-132,340</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-13.23 Cr</t>
+            <t>-82,749</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.27 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>81.68</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 05.09.2026</t>
+          <t>GSU FR Fund Wise - As On 25.09.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4531,19 +4531,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>319,136</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>31.91 Cr</t>
+            <t>368,727</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.87 Cr</t>
           </r>
         </is>
       </c>
@@ -4554,30 +4554,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>132,465</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>13.25 Cr</t>
+            <t>82,874</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.29 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>18.35</t>
         </is>
       </c>
     </row>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 25." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 25.09.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 25.09." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.10.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.10." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 25.09.2026</t>
+          <t>Open Line FR Report - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -593,19 +593,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>81,555</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.16 Cr</t>
+            <t>80,418</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>8.04 Cr</t>
           </r>
         </is>
       </c>
@@ -616,25 +616,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-79,348</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.93 Cr</t>
+            <t>-80,485</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-8.05 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>49.98</t>
         </is>
       </c>
     </row>
@@ -679,19 +679,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,767</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.28 Cr</t>
+            <t>12,890</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.29 Cr</t>
           </r>
         </is>
       </c>
@@ -702,25 +702,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-19,460</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.95 Cr</t>
+            <t>-19,337</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.93 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>40.00</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>64,676</t>
+            <t>64,681</t>
           </r>
           <r>
             <t>
@@ -788,7 +788,7 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-55,642</t>
+            <t>-55,637</t>
           </r>
           <r>
             <t>
@@ -806,7 +806,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>53.76</t>
         </is>
       </c>
     </row>
@@ -851,19 +851,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>379,202</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.92 Cr</t>
+            <t>379,598</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.96 Cr</t>
           </r>
         </is>
       </c>
@@ -874,25 +874,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-128,218</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.82 Cr</t>
+            <t>-127,822</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-12.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>74.81</t>
         </is>
       </c>
     </row>
@@ -937,19 +937,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,805,865</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>380.59 Cr</t>
+            <t>4,286,712</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>428.67 Cr</t>
           </r>
         </is>
       </c>
@@ -960,25 +960,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>843,070</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>84.31 Cr</t>
+            <t>1,323,917</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>132.39 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>128.46</t>
+          <t>144.68</t>
         </is>
       </c>
     </row>
@@ -1023,19 +1023,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>183,938</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>18.39 Cr</t>
+            <t>187,787</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.78 Cr</t>
           </r>
         </is>
       </c>
@@ -1046,25 +1046,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>51,671</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.17 Cr</t>
+            <t>55,520</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>139.07</t>
+          <t>141.98</t>
         </is>
       </c>
     </row>
@@ -1109,19 +1109,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>140,407</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.04 Cr</t>
+            <t>251,247</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>25.12 Cr</t>
           </r>
         </is>
       </c>
@@ -1132,25 +1132,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-382,436</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-38.24 Cr</t>
+            <t>-271,596</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-27.16 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>48.05</t>
         </is>
       </c>
     </row>
@@ -1367,19 +1367,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>25,991</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.60 Cr</t>
+            <t>29,430</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.94 Cr</t>
           </r>
         </is>
       </c>
@@ -1390,25 +1390,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-14,381</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.44 Cr</t>
+            <t>-10,942</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.09 Cr</t>
           </r>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>64.38</t>
+          <t>72.90</t>
         </is>
       </c>
     </row>
@@ -1539,19 +1539,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>71,111</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.11 Cr</t>
+            <t>72,216</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.22 Cr</t>
           </r>
         </is>
       </c>
@@ -1562,25 +1562,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-26,389</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.64 Cr</t>
+            <t>-25,284</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-2.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>72.93</t>
+          <t>74.07</t>
         </is>
       </c>
     </row>
@@ -1625,19 +1625,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>147,126</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>14.71 Cr</t>
+            <t>155,585</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>15.56 Cr</t>
           </r>
         </is>
       </c>
@@ -1648,25 +1648,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-163,786</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-16.38 Cr</t>
+            <t>-155,327</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-15.53 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>50.04</t>
         </is>
       </c>
     </row>
@@ -1797,19 +1797,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>112,585</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.26 Cr</t>
+            <t>113,720</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.37 Cr</t>
           </r>
         </is>
       </c>
@@ -1820,25 +1820,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-203,148</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.31 Cr</t>
+            <t>-202,013</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.20 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.02</t>
         </is>
       </c>
     </row>
@@ -2047,19 +2047,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,135,999</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>513.60 Cr</t>
+            <t>5,745,060</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>574.51 Cr</t>
           </r>
         </is>
       </c>
@@ -2070,25 +2070,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-498,880</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-49.89 Cr</t>
+            <t>110,181</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.02 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>101.96</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2118,7 +2118,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 25.09.2026</t>
+          <t>Open Line FR Fund Wise - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2215,19 +2215,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>457,028</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>45.70 Cr</t>
+            <t>494,859</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>49.49 Cr</t>
           </r>
         </is>
       </c>
@@ -2238,30 +2238,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>588,503</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>58.85 Cr</t>
+            <t>550,672</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>55.07 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>47.33</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>56.29</t>
+          <t>52.67</t>
         </is>
       </c>
     </row>
@@ -2301,19 +2301,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>21,238</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.12 Cr</t>
+            <t>22,085</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.21 Cr</t>
           </r>
         </is>
       </c>
@@ -2324,30 +2324,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,994</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.90 Cr</t>
+            <t>18,147</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.81 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>52.79</t>
+          <t>54.89</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>45.11</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2559,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>3,844,908</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>384.49 Cr</t>
+            <t>4,324,735</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>432.47 Cr</t>
           </r>
         </is>
       </c>
@@ -2582,30 +2582,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-727,393</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-72.74 Cr</t>
+            <t>-1,207,220</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-120.72 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>123.33</t>
+          <t>138.72</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-38.72</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>794,366</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>79.44 Cr</t>
+            <t>884,922</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>88.49 Cr</t>
           </r>
         </is>
       </c>
@@ -2754,30 +2754,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>506,643</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>50.66 Cr</t>
+            <t>416,087</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>41.61 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>31.98</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 25.09.2026</t>
+          <t>GSU FR Report - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3941,19 +3941,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>366,679</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.67 Cr</t>
+            <t>372,864</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.29 Cr</t>
           </r>
         </is>
       </c>
@@ -3964,25 +3964,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-79,921</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.99 Cr</t>
+            <t>-73,736</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.37 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>82.10</t>
+          <t>83.49</t>
         </is>
       </c>
     </row>
@@ -4363,19 +4363,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>368,854</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.89 Cr</t>
+            <t>375,039</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.50 Cr</t>
           </r>
         </is>
       </c>
@@ -4386,25 +4386,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-82,749</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-8.27 Cr</t>
+            <t>-76,564</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-7.66 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>81.68</t>
+          <t>83.05</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 25.09.2026</t>
+          <t>GSU FR Fund Wise - As On 05.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4531,19 +4531,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>368,727</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>36.87 Cr</t>
+            <t>374,912</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.49 Cr</t>
           </r>
         </is>
       </c>
@@ -4554,30 +4554,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>82,874</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.29 Cr</t>
+            <t>76,689</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.67 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>81.65</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>16.98</t>
         </is>
       </c>
     </row>

--- a/exports/FR_Budget_Status.xlsx
+++ b/exports/FR_Budget_Status.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 05." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Report - As On 19." sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Line FR Fund Wise - As On " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 05.10.202" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 05.10." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Report - As On 19.10.202" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSU FR Fund Wise - As On 19.10." sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Report - As On 05.10.2026</t>
+          <t>Open Line FR Report - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -593,19 +593,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>80,418</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>8.04 Cr</t>
+            <t>99,183</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>9.92 Cr</t>
           </r>
         </is>
       </c>
@@ -616,25 +616,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-80,485</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-8.05 Cr</t>
+            <t>-61,720</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-6.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>61.64</t>
         </is>
       </c>
     </row>
@@ -679,19 +679,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>12,890</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.29 Cr</t>
+            <t>13,774</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.38 Cr</t>
           </r>
         </is>
       </c>
@@ -702,25 +702,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-19,337</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-1.93 Cr</t>
+            <t>-18,453</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.85 Cr</t>
           </r>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>42.74</t>
         </is>
       </c>
     </row>
@@ -851,19 +851,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>379,598</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.96 Cr</t>
+            <t>398,602</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.86 Cr</t>
           </r>
         </is>
       </c>
@@ -874,25 +874,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-127,822</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-12.78 Cr</t>
+            <t>-108,818</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-10.88 Cr</t>
           </r>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>78.55</t>
         </is>
       </c>
     </row>
@@ -937,19 +937,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,286,712</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>428.67 Cr</t>
+            <t>4,376,267</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>437.63 Cr</t>
           </r>
         </is>
       </c>
@@ -960,25 +960,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>1,323,917</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>132.39 Cr</t>
+            <t>1,413,472</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>141.35 Cr</t>
           </r>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>144.68</t>
+          <t>147.71</t>
         </is>
       </c>
     </row>
@@ -1023,19 +1023,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>187,787</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>18.78 Cr</t>
+            <t>187,876</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>18.79 Cr</t>
           </r>
         </is>
       </c>
@@ -1046,25 +1046,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>55,520</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>5.55 Cr</t>
+            <t>55,609</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.56 Cr</t>
           </r>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>141.98</t>
+          <t>142.04</t>
         </is>
       </c>
     </row>
@@ -1109,19 +1109,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>251,247</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>25.12 Cr</t>
+            <t>307,683</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>30.77 Cr</t>
           </r>
         </is>
       </c>
@@ -1132,25 +1132,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-271,596</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-27.16 Cr</t>
+            <t>-215,160</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-21.52 Cr</t>
           </r>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>48.05</t>
+          <t>58.85</t>
         </is>
       </c>
     </row>
@@ -1195,19 +1195,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>105,095</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>10.51 Cr</t>
+            <t>107,120</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>10.71 Cr</t>
           </r>
         </is>
       </c>
@@ -1218,25 +1218,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-202,748</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.27 Cr</t>
+            <t>-200,723</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-20.07 Cr</t>
           </r>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>34.80</t>
         </is>
       </c>
     </row>
@@ -1453,19 +1453,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,681</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.57 Cr</t>
+            <t>8,185</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.82 Cr</t>
           </r>
         </is>
       </c>
@@ -1476,25 +1476,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-48,021</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-4.80 Cr</t>
+            <t>-45,517</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-4.55 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>15.24</t>
         </is>
       </c>
     </row>
@@ -1539,19 +1539,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>72,216</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.22 Cr</t>
+            <t>79,886</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>7.99 Cr</t>
           </r>
         </is>
       </c>
@@ -1562,25 +1562,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-25,284</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-2.53 Cr</t>
+            <t>-17,614</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-1.76 Cr</t>
           </r>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>81.93</t>
         </is>
       </c>
     </row>
@@ -1625,19 +1625,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>155,585</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>15.56 Cr</t>
+            <t>209,920</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>20.99 Cr</t>
           </r>
         </is>
       </c>
@@ -1648,25 +1648,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-155,327</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-15.53 Cr</t>
+            <t>-100,992</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-10.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>67.52</t>
         </is>
       </c>
     </row>
@@ -1797,19 +1797,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>113,720</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.37 Cr</t>
+            <t>124,015</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>12.40 Cr</t>
           </r>
         </is>
       </c>
@@ -1820,25 +1820,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-202,013</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-20.20 Cr</t>
+            <t>-191,718</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-19.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>36.02</t>
+          <t>39.28</t>
         </is>
       </c>
     </row>
@@ -2047,19 +2047,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>5,745,060</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>574.51 Cr</t>
+            <t>6,006,622</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>600.66 Cr</t>
           </r>
         </is>
       </c>
@@ -2070,25 +2070,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>110,181</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.02 Cr</t>
+            <t>371,743</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>37.17 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>106.60</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Line FR Fund Wise - As On 05.10.2026</t>
+          <t>Open Line FR Fund Wise - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2215,19 +2215,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>494,859</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>49.49 Cr</t>
+            <t>621,086</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>62.11 Cr</t>
           </r>
         </is>
       </c>
@@ -2238,30 +2238,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>550,672</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>55.07 Cr</t>
+            <t>424,445</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>42.44 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>59.40</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>52.67</t>
+          <t>40.60</t>
         </is>
       </c>
     </row>
@@ -2301,19 +2301,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>22,085</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>2.21 Cr</t>
+            <t>25,605</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2.56 Cr</t>
           </r>
         </is>
       </c>
@@ -2324,30 +2324,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,147</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.81 Cr</t>
+            <t>14,627</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.46 Cr</t>
           </r>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>54.89</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>45.11</t>
+          <t>36.36</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2387,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>18,459</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>1.85 Cr</t>
+            <t>18,607</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1.86 Cr</t>
           </r>
         </is>
       </c>
@@ -2410,30 +2410,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>112,133</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>11.21 Cr</t>
+            <t>111,985</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>11.20 Cr</t>
           </r>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>85.87</t>
+          <t>85.75</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2559,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>4,324,735</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>432.47 Cr</t>
+            <t>4,405,363</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>440.54 Cr</t>
           </r>
         </is>
       </c>
@@ -2582,30 +2582,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-1,207,220</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-120.72 Cr</t>
+            <t>-1,287,848</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-128.78 Cr</t>
           </r>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>138.72</t>
+          <t>141.31</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>-38.72</t>
+          <t>-41.31</t>
         </is>
       </c>
     </row>
@@ -2731,19 +2731,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>884,922</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>88.49 Cr</t>
+            <t>935,961</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>93.60 Cr</t>
           </r>
         </is>
       </c>
@@ -2754,30 +2754,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>416,087</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>41.61 Cr</t>
+            <t>365,048</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>36.50 Cr</t>
           </r>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>28.06</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Report - As On 05.10.2026</t>
+          <t>GSU FR Report - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3769,19 +3769,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>2,048</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0.20 Cr</t>
+            <t>4,035</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0.40 Cr</t>
           </r>
         </is>
       </c>
@@ -3792,25 +3792,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-2,953</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-0.30 Cr</t>
+            <t>-966</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-0.10 Cr</t>
           </r>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>80.68</t>
         </is>
       </c>
     </row>
@@ -3941,19 +3941,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>372,864</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.29 Cr</t>
+            <t>395,318</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.53 Cr</t>
           </r>
         </is>
       </c>
@@ -3964,25 +3964,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-73,736</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.37 Cr</t>
+            <t>-51,282</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.13 Cr</t>
           </r>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>83.49</t>
+          <t>88.52</t>
         </is>
       </c>
     </row>
@@ -4363,19 +4363,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>375,039</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.50 Cr</t>
+            <t>399,480</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.95 Cr</t>
           </r>
         </is>
       </c>
@@ -4386,25 +4386,25 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>-76,564</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>-7.66 Cr</t>
+            <t>-52,123</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>-5.21 Cr</t>
           </r>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>88.46</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSU FR Fund Wise - As On 05.10.2026</t>
+          <t>GSU FR Fund Wise - As On 19.10.2026</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -4531,19 +4531,19 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>374,912</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>37.49 Cr</t>
+            <t>399,353</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>39.94 Cr</t>
           </r>
         </is>
       </c>
@@ -4554,30 +4554,30 @@
               <rFont val="Times New Roman"/>
               <sz val="11"/>
             </rPr>
-            <t>76,689</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <color rgb="FF006F78"/>
-              <sz val="9"/>
-            </rPr>
-            <t>7.67 Cr</t>
+            <t>52,248</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <color rgb="FF006F78"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5.22 Cr</t>
           </r>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>11.57</t>
         </is>
       </c>
     </row>
